--- a/data/dividends_info_20260814.xlsx
+++ b/data/dividends_info_20260814.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>46.90000152587891</v>
+        <v>46.65499877929688</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1918976483408833</v>
+        <v>0.1929053742467087</v>
       </c>
       <c r="J2" t="n">
         <v>213</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>66.84999847412109</v>
+        <v>66.94999694824219</v>
       </c>
       <c r="I3" t="n">
-        <v>1.047120442749125</v>
+        <v>1.045556433021434</v>
       </c>
       <c r="J3" t="n">
         <v>192</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>9.399999618530273</v>
+        <v>9.300000190734863</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6382978982437579</v>
+        <v>0.6451612770908873</v>
       </c>
       <c r="J4" t="n">
         <v>122</v>
@@ -663,12 +663,8 @@
           <t>IT0004587470</t>
         </is>
       </c>
-      <c r="H5" t="n">
-        <v>0.4979999959468842</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0.8032128579428007</v>
-      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="n">
         <v>122</v>
       </c>
@@ -711,10 +707,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>46.90999984741211</v>
+        <v>46.65499877929688</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1918567475863359</v>
+        <v>0.1929053742467087</v>
       </c>
       <c r="J6" t="n">
         <v>122</v>
@@ -758,10 +754,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.150000095367432</v>
+        <v>2.125</v>
       </c>
       <c r="I7" t="n">
-        <v>3.58139518997746</v>
+        <v>3.623529411764706</v>
       </c>
       <c r="J7" t="n">
         <v>101</v>
@@ -805,10 +801,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>23.76000022888184</v>
+        <v>23.69499969482422</v>
       </c>
       <c r="I8" t="n">
-        <v>1.136363625416962</v>
+        <v>1.139480917819877</v>
       </c>
       <c r="J8" t="n">
         <v>101</v>
@@ -852,10 +848,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>22.85000038146973</v>
+        <v>23.21999931335449</v>
       </c>
       <c r="I9" t="n">
-        <v>2.5820568496728</v>
+        <v>2.540913081167379</v>
       </c>
       <c r="J9" t="n">
         <v>101</v>
@@ -899,10 +895,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>5.840000152587891</v>
+        <v>5.889999866485596</v>
       </c>
       <c r="I10" t="n">
-        <v>3.424657444766908</v>
+        <v>3.395585815510971</v>
       </c>
       <c r="J10" t="n">
         <v>94</v>
@@ -946,10 +942,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>10.67000007629395</v>
+        <v>10.38000011444092</v>
       </c>
       <c r="I11" t="n">
-        <v>4.311152733934878</v>
+        <v>4.431599180428105</v>
       </c>
       <c r="J11" t="n">
         <v>73</v>
@@ -993,10 +989,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>7.599999904632568</v>
+        <v>7.5</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7894736941171157</v>
+        <v>0.8</v>
       </c>
       <c r="J12" t="n">
         <v>66</v>
@@ -1039,12 +1035,8 @@
           <t>IT0004587470</t>
         </is>
       </c>
-      <c r="H13" t="n">
-        <v>0.4939999878406525</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0.8097166191206999</v>
-      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="n">
         <v>66</v>
       </c>
@@ -1134,10 +1126,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>5.019999980926514</v>
+        <v>4.96999979019165</v>
       </c>
       <c r="I15" t="n">
-        <v>0.7569721144298999</v>
+        <v>0.7645875574279384</v>
       </c>
       <c r="J15" t="n">
         <v>45</v>
@@ -1181,10 +1173,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>23.76000022888184</v>
+        <v>23.69499969482422</v>
       </c>
       <c r="I16" t="n">
-        <v>1.136363625416962</v>
+        <v>1.139480917819877</v>
       </c>
       <c r="J16" t="n">
         <v>38</v>
@@ -1228,10 +1220,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>1.983999967575073</v>
+        <v>1.973000049591064</v>
       </c>
       <c r="I17" t="n">
-        <v>2.872983917921519</v>
+        <v>2.88900144791249</v>
       </c>
       <c r="J17" t="n">
         <v>38</v>
@@ -1275,10 +1267,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>46.90999984741211</v>
+        <v>46.65499877929688</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1918567475863359</v>
+        <v>0.1929053742467087</v>
       </c>
       <c r="J18" t="n">
         <v>38</v>
@@ -1322,10 +1314,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>93.90000152587891</v>
+        <v>94.65000152587891</v>
       </c>
       <c r="I19" t="n">
-        <v>1.416400402968525</v>
+        <v>1.40517694512277</v>
       </c>
       <c r="J19" t="n">
         <v>38</v>
@@ -1369,10 +1361,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>5.739999771118164</v>
+        <v>5.800000190734863</v>
       </c>
       <c r="I20" t="n">
-        <v>5.226481044642261</v>
+        <v>5.172413623006964</v>
       </c>
       <c r="J20" t="n">
         <v>31</v>
@@ -1415,12 +1407,8 @@
           <t>IT0004587470</t>
         </is>
       </c>
-      <c r="H21" t="n">
-        <v>0.4939999878406525</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0.8097166191206999</v>
-      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="n">
         <v>10</v>
       </c>
@@ -1463,10 +1451,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>2.640000104904175</v>
+        <v>2.5</v>
       </c>
       <c r="I22" t="n">
-        <v>8.333333002196431</v>
+        <v>8.799999999999999</v>
       </c>
       <c r="J22" t="n">
         <v>-4</v>
@@ -1510,10 +1498,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>5.019999980926514</v>
+        <v>4.96999979019165</v>
       </c>
       <c r="I23" t="n">
-        <v>0.7569721144298999</v>
+        <v>0.7645875574279384</v>
       </c>
       <c r="J23" t="n">
         <v>-11</v>
@@ -1604,10 +1592,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>2.640000104904175</v>
+        <v>2.619999885559082</v>
       </c>
       <c r="I25" t="n">
-        <v>5.604886140918198</v>
+        <v>5.647672002414033</v>
       </c>
       <c r="J25" t="n">
         <v>-11</v>
@@ -1698,10 +1686,10 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>4.199999809265137</v>
+        <v>4.230000019073486</v>
       </c>
       <c r="I27" t="n">
-        <v>3.333333484710216</v>
+        <v>3.30969265647107</v>
       </c>
       <c r="J27" t="n">
         <v>-25</v>
@@ -1745,10 +1733,10 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>9.543000221252441</v>
+        <v>9.494999885559082</v>
       </c>
       <c r="I28" t="n">
-        <v>2.72451004895688</v>
+        <v>2.738283340007547</v>
       </c>
       <c r="J28" t="n">
         <v>-25</v>
@@ -1792,10 +1780,10 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>13.68000030517578</v>
+        <v>13.81999969482422</v>
       </c>
       <c r="I29" t="n">
-        <v>4.385964814437847</v>
+        <v>4.341534104553622</v>
       </c>
       <c r="J29" t="n">
         <v>-25</v>
@@ -1839,10 +1827,10 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>2.706000089645386</v>
+        <v>2.687999963760376</v>
       </c>
       <c r="I30" t="n">
-        <v>8.130081031476626</v>
+        <v>8.184523919867585</v>
       </c>
       <c r="J30" t="n">
         <v>-25</v>
@@ -1885,12 +1873,8 @@
           <t>IT0004587470</t>
         </is>
       </c>
-      <c r="H31" t="n">
-        <v>0.4939999878406525</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0.8097166191206999</v>
-      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
       <c r="J31" t="n">
         <v>-25</v>
       </c>
@@ -1933,10 +1917,10 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>6.735000133514404</v>
+        <v>6.695000171661377</v>
       </c>
       <c r="I32" t="n">
-        <v>1.484780965369021</v>
+        <v>1.493651940791285</v>
       </c>
       <c r="J32" t="n">
         <v>-25</v>
